--- a/data/dividends_info_20260812.xlsx
+++ b/data/dividends_info_20260812.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>48.2400016784668</v>
+        <v>48.03499984741211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1865671576876704</v>
+        <v>0.1873633814632951</v>
       </c>
       <c r="J2" t="n">
         <v>215</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67.40000152587891</v>
+        <v>67.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.038575644143313</v>
+        <v>1.037037037037037</v>
       </c>
       <c r="J3" t="n">
         <v>194</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.420000076293945</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6369426700005446</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J4" t="n">
         <v>124</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4939999878406525</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8097166191206999</v>
       </c>
       <c r="J5" t="n">
         <v>124</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48.2400016784668</v>
+        <v>48.03499984741211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1865671576876704</v>
+        <v>0.1873633814632951</v>
       </c>
       <c r="J6" t="n">
         <v>124</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.150000095367432</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="I7" t="n">
-        <v>3.58139518997746</v>
+        <v>3.649289280960038</v>
       </c>
       <c r="J7" t="n">
         <v>103</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.9950008392334</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I8" t="n">
-        <v>1.125234384482839</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J8" t="n">
         <v>103</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.19000053405762</v>
+        <v>23.09000015258789</v>
       </c>
       <c r="I9" t="n">
-        <v>2.54420002765203</v>
+        <v>2.555218692512108</v>
       </c>
       <c r="J9" t="n">
         <v>103</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.889999866485596</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I10" t="n">
-        <v>3.395585815510971</v>
+        <v>3.442340825640675</v>
       </c>
       <c r="J10" t="n">
         <v>96</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.84000015258789</v>
+        <v>10.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.243542375690666</v>
+        <v>4.279069767441861</v>
       </c>
       <c r="J11" t="n">
         <v>75</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4939999878406525</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8097166191206999</v>
       </c>
       <c r="J13" t="n">
         <v>68</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.039999961853027</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I15" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J15" t="n">
         <v>47</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.9950008392334</v>
+        <v>23.86000061035156</v>
       </c>
       <c r="I16" t="n">
-        <v>1.125234384482839</v>
+        <v>1.131600976920603</v>
       </c>
       <c r="J16" t="n">
         <v>40</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.988999962806702</v>
+        <v>1.960999965667725</v>
       </c>
       <c r="I17" t="n">
-        <v>2.865761742879402</v>
+        <v>2.906680316059638</v>
       </c>
       <c r="J17" t="n">
         <v>40</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48.2400016784668</v>
+        <v>48.03499984741211</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1865671576876704</v>
+        <v>0.1873633814632951</v>
       </c>
       <c r="J18" t="n">
         <v>40</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>96.09999847412109</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.383975047989369</v>
+        <v>1.412639382309967</v>
       </c>
       <c r="J19" t="n">
         <v>40</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.760000228881836</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I20" t="n">
-        <v>5.208333126372769</v>
+        <v>5.190311230281897</v>
       </c>
       <c r="J20" t="n">
         <v>33</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4939999878406525</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8097166191206999</v>
       </c>
       <c r="J21" t="n">
         <v>12</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.779999971389771</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I22" t="n">
-        <v>7.913669146191328</v>
+        <v>7.801418624397476</v>
       </c>
       <c r="J22" t="n">
         <v>-2</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.039999961853027</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I23" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J23" t="n">
         <v>-9</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.599999904632568</v>
+        <v>2.640000104904175</v>
       </c>
       <c r="I25" t="n">
-        <v>5.69111559336426</v>
+        <v>5.604886140918198</v>
       </c>
       <c r="J25" t="n">
         <v>-9</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6.059999942779541</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I26" t="n">
-        <v>4.125412580207591</v>
+        <v>4.159733618621054</v>
       </c>
       <c r="J26" t="n">
         <v>-16</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.239999771118164</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="I27" t="n">
-        <v>3.301886970693857</v>
+        <v>3.30969265647107</v>
       </c>
       <c r="J27" t="n">
         <v>-23</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.786999702453613</v>
+        <v>9.720999717712402</v>
       </c>
       <c r="I28" t="n">
-        <v>2.656585346935462</v>
+        <v>2.674622030142231</v>
       </c>
       <c r="J28" t="n">
         <v>-23</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.84000015258789</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="I29" t="n">
-        <v>4.335260067810101</v>
+        <v>4.366812299816886</v>
       </c>
       <c r="J29" t="n">
         <v>-23</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.670000076293945</v>
+        <v>2.676000118255615</v>
       </c>
       <c r="I30" t="n">
-        <v>8.23970013908643</v>
+        <v>8.221225346709245</v>
       </c>
       <c r="J30" t="n">
         <v>-23</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.492000013589859</v>
+        <v>0.4939999878406525</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8130081076246635</v>
+        <v>0.8097166191206999</v>
       </c>
       <c r="J31" t="n">
         <v>-23</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.425000190734863</v>
+        <v>6.505000114440918</v>
       </c>
       <c r="I32" t="n">
-        <v>3.735408449420604</v>
+        <v>3.689469573831471</v>
       </c>
       <c r="J32" t="n">
         <v>-23</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18.39999961853027</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I33" t="n">
-        <v>2.04347830323506</v>
+        <v>1.989418029571574</v>
       </c>
       <c r="J33" t="n">
         <v>-23</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.670000076293945</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I35" t="n">
-        <v>2.116402087924397</v>
+        <v>2.120141399913057</v>
       </c>
       <c r="J35" t="n">
         <v>-30</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.960000038146973</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I37" t="n">
-        <v>5.067567502259338</v>
+        <v>4.934210588231972</v>
       </c>
       <c r="J37" t="n">
         <v>-30</v>
@@ -3221,180 +3221,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Altea Green Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CEMBRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EUROTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pharmanutra S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>